--- a/No_Entendidos/output/no_entendimiento_detalle_agosto_2026.xlsx
+++ b/No_Entendidos/output/no_entendimiento_detalle_agosto_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="No Entendimiento" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No Entendimiento" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.467</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="6">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.124</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="7">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.045</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="8">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.221</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="9">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="10">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.073</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="11">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="12">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.636</v>
+        <v>0.5859999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.221</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="18">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>0.143</v>
+        <v>0.175</v>
       </c>
     </row>
   </sheetData>
